--- a/satisfaction_surveys/011_inclusive_public_space_design_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/011_inclusive_public_space_design_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,8 +803,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'wheelchair_accessible_entrances'}</t>
+          <t>wheelchair_accessible_entrances</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Wheelchair Accessible Entrances'}</t>
+          <t>Wheelchair Accessible Entrances</t>
         </is>
       </c>
     </row>
@@ -883,12 +883,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'accessible_restrooms'}</t>
+          <t>accessible_restrooms</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Accessible Restrooms'}</t>
+          <t>Accessible Restrooms</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'sign_language_interpretation'}</t>
+          <t>sign_language_interpretation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Sign Language Interpretation'}</t>
+          <t>Sign Language Interpretation</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'assistive_technology'}</t>
+          <t>assistive_technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Assistive Technology'}</t>
+          <t>Assistive Technology</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'wheelchairs'}</t>
+          <t>wheelchairs</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Wheelchairs'}</t>
+          <t>Wheelchairs</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'stairs'}</t>
+          <t>stairs</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Stairs'}</t>
+          <t>Stairs</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'elevators'}</t>
+          <t>elevators</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Elevators'}</t>
+          <t>Elevators</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'wheelchair'}</t>
+          <t>wheelchair</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Wheelchair'}</t>
+          <t>Wheelchair</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'sign_language'}</t>
+          <t>sign_language</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Sign Language'}</t>
+          <t>Sign Language</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'braille'}</t>
+          <t>braille</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Braille'}</t>
+          <t>Braille</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'large_print_materials'}</t>
+          <t>large_print_materials</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Large Print Materials'}</t>
+          <t>Large Print Materials</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'architectural'}</t>
+          <t>architectural</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Architectural'}</t>
+          <t>Architectural</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'physical'}</t>
+          <t>physical</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Physical'}</t>
+          <t>Physical</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'service_animal'}</t>
+          <t>service_animal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Service Animal'}</t>
+          <t>Service Animal</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'sign_language'}</t>
+          <t>sign_language</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Sign Language'}</t>
+          <t>Sign Language</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'visual_assistance'}</t>
+          <t>visual_assistance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Visual Assistance'}</t>
+          <t>Visual Assistance</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'braille'}</t>
+          <t>braille</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Braille'}</t>
+          <t>Braille</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'large_print'}</t>
+          <t>large_print</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Large Print'}</t>
+          <t>Large Print</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'sign_language'}</t>
+          <t>sign_language</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Sign Language'}</t>
+          <t>Sign Language</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'wheelchair'}</t>
+          <t>wheelchair</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Wheelchair'}</t>
+          <t>Wheelchair</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'service_animal'}</t>
+          <t>service_animal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Service Animal'}</t>
+          <t>Service Animal</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'visual_assistance'}</t>
+          <t>visual_assistance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Visual Assistance'}</t>
+          <t>Visual Assistance</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'wheelchairs'}</t>
+          <t>wheelchairs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Wheelchairs'}</t>
+          <t>Wheelchairs</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'wheelchair_accessible'}</t>
+          <t>wheelchair_accessible</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Wheelchair Accessible'}</t>
+          <t>Wheelchair Accessible</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'accessible_restrooms'}</t>
+          <t>accessible_restrooms</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Accessible Restrooms'}</t>
+          <t>Accessible Restrooms</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'wheelchair'}</t>
+          <t>wheelchair</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Wheelchair'}</t>
+          <t>Wheelchair</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'service_animal'}</t>
+          <t>service_animal</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Service Animal'}</t>
+          <t>Service Animal</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'service_animal_access'}</t>
+          <t>service_animal_access</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Service Animal Access'}</t>
+          <t>Service Animal Access</t>
         </is>
       </c>
     </row>
